--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ruiro\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106D94E8-A957-4B1B-8644-5F79E7E3A121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E72F94-189A-411C-9726-91763DF3CA43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Leagues" sheetId="10" r:id="rId1"/>
@@ -63491,7 +63491,7 @@
         <v>6</v>
       </c>
       <c r="E1846" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1846" t="s">
         <v>116</v>
@@ -63526,7 +63526,7 @@
         <v>6</v>
       </c>
       <c r="E1847" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1847" t="s">
         <v>116</v>
@@ -63558,7 +63558,7 @@
         <v>6</v>
       </c>
       <c r="E1848" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1848" t="s">
         <v>116</v>
@@ -63590,7 +63590,7 @@
         <v>6</v>
       </c>
       <c r="E1849" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1849" t="s">
         <v>116</v>
@@ -63622,7 +63622,7 @@
         <v>6</v>
       </c>
       <c r="E1850" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1850" t="s">
         <v>116</v>
@@ -63654,7 +63654,7 @@
         <v>6</v>
       </c>
       <c r="E1851" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1851" t="s">
         <v>116</v>
@@ -63686,7 +63686,7 @@
         <v>6</v>
       </c>
       <c r="E1852" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1852" t="s">
         <v>116</v>
@@ -63718,7 +63718,7 @@
         <v>6</v>
       </c>
       <c r="E1853" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1853" t="s">
         <v>116</v>
@@ -63750,7 +63750,7 @@
         <v>6</v>
       </c>
       <c r="E1854" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1854" t="s">
         <v>116</v>
@@ -63782,7 +63782,7 @@
         <v>6</v>
       </c>
       <c r="E1855" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1855" t="s">
         <v>116</v>
@@ -63814,7 +63814,7 @@
         <v>6</v>
       </c>
       <c r="E1856" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1856" t="s">
         <v>116</v>
@@ -63846,7 +63846,7 @@
         <v>6</v>
       </c>
       <c r="E1857" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1857" t="s">
         <v>116</v>
@@ -63878,7 +63878,7 @@
         <v>6</v>
       </c>
       <c r="E1858" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1858" t="s">
         <v>116</v>
@@ -63910,7 +63910,7 @@
         <v>6</v>
       </c>
       <c r="E1859" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1859" t="s">
         <v>116</v>
@@ -63942,7 +63942,7 @@
         <v>6</v>
       </c>
       <c r="E1860" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1860" t="s">
         <v>116</v>
@@ -63974,7 +63974,7 @@
         <v>6</v>
       </c>
       <c r="E1861" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1861" t="s">
         <v>116</v>
@@ -64006,7 +64006,7 @@
         <v>6</v>
       </c>
       <c r="E1862" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1862" t="s">
         <v>116</v>
@@ -64038,7 +64038,7 @@
         <v>6</v>
       </c>
       <c r="E1863" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1863" t="s">
         <v>116</v>
@@ -64073,7 +64073,7 @@
         <v>6</v>
       </c>
       <c r="E1864" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1864" t="s">
         <v>116</v>
@@ -64105,7 +64105,7 @@
         <v>6</v>
       </c>
       <c r="E1865" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1865" t="s">
         <v>116</v>
@@ -64137,7 +64137,7 @@
         <v>6</v>
       </c>
       <c r="E1866" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1866" t="s">
         <v>116</v>
@@ -64172,7 +64172,7 @@
         <v>6</v>
       </c>
       <c r="E1867" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F1867" t="s">
         <v>116</v>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ruiro\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E72F94-189A-411C-9726-91763DF3CA43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8606141A-2CDE-4C30-951C-61039481B922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62784,7 +62784,7 @@
         <v>204</v>
       </c>
       <c r="D1824">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1824" t="s">
         <v>207</v>
@@ -62816,7 +62816,7 @@
         <v>204</v>
       </c>
       <c r="D1825">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1825" t="s">
         <v>207</v>
@@ -62848,7 +62848,7 @@
         <v>204</v>
       </c>
       <c r="D1826">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1826" t="s">
         <v>207</v>
@@ -62880,7 +62880,7 @@
         <v>204</v>
       </c>
       <c r="D1827">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1827" t="s">
         <v>207</v>
@@ -62912,7 +62912,7 @@
         <v>204</v>
       </c>
       <c r="D1828">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1828" t="s">
         <v>207</v>
@@ -62944,7 +62944,7 @@
         <v>204</v>
       </c>
       <c r="D1829">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1829" t="s">
         <v>207</v>
@@ -62976,7 +62976,7 @@
         <v>204</v>
       </c>
       <c r="D1830">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1830" t="s">
         <v>207</v>
@@ -63008,7 +63008,7 @@
         <v>204</v>
       </c>
       <c r="D1831">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1831" t="s">
         <v>207</v>
@@ -63040,7 +63040,7 @@
         <v>204</v>
       </c>
       <c r="D1832">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1832" t="s">
         <v>207</v>
@@ -63072,7 +63072,7 @@
         <v>204</v>
       </c>
       <c r="D1833">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1833" t="s">
         <v>207</v>
@@ -63104,7 +63104,7 @@
         <v>204</v>
       </c>
       <c r="D1834">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1834" t="s">
         <v>207</v>
@@ -63136,7 +63136,7 @@
         <v>204</v>
       </c>
       <c r="D1835">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1835" t="s">
         <v>207</v>
@@ -63168,7 +63168,7 @@
         <v>204</v>
       </c>
       <c r="D1836">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1836" t="s">
         <v>207</v>
@@ -63200,7 +63200,7 @@
         <v>204</v>
       </c>
       <c r="D1837">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1837" t="s">
         <v>207</v>
@@ -63232,7 +63232,7 @@
         <v>204</v>
       </c>
       <c r="D1838">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1838" t="s">
         <v>207</v>
@@ -63264,7 +63264,7 @@
         <v>204</v>
       </c>
       <c r="D1839">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1839" t="s">
         <v>207</v>
@@ -63296,7 +63296,7 @@
         <v>204</v>
       </c>
       <c r="D1840">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1840" t="s">
         <v>207</v>
@@ -63328,7 +63328,7 @@
         <v>204</v>
       </c>
       <c r="D1841">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1841" t="s">
         <v>207</v>
@@ -63360,7 +63360,7 @@
         <v>204</v>
       </c>
       <c r="D1842">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1842" t="s">
         <v>207</v>
@@ -63392,7 +63392,7 @@
         <v>204</v>
       </c>
       <c r="D1843">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1843" t="s">
         <v>207</v>
@@ -63424,7 +63424,7 @@
         <v>204</v>
       </c>
       <c r="D1844">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1844" t="s">
         <v>207</v>
@@ -63456,7 +63456,7 @@
         <v>204</v>
       </c>
       <c r="D1845">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1845" t="s">
         <v>207</v>
@@ -63488,7 +63488,7 @@
         <v>204</v>
       </c>
       <c r="D1846">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1846" t="s">
         <v>206</v>
@@ -63523,7 +63523,7 @@
         <v>204</v>
       </c>
       <c r="D1847">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1847" t="s">
         <v>206</v>
@@ -63555,7 +63555,7 @@
         <v>204</v>
       </c>
       <c r="D1848">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1848" t="s">
         <v>206</v>
@@ -63587,7 +63587,7 @@
         <v>204</v>
       </c>
       <c r="D1849">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1849" t="s">
         <v>206</v>
@@ -63619,7 +63619,7 @@
         <v>204</v>
       </c>
       <c r="D1850">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1850" t="s">
         <v>206</v>
@@ -63651,7 +63651,7 @@
         <v>204</v>
       </c>
       <c r="D1851">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1851" t="s">
         <v>206</v>
@@ -63683,7 +63683,7 @@
         <v>204</v>
       </c>
       <c r="D1852">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1852" t="s">
         <v>206</v>
@@ -63715,7 +63715,7 @@
         <v>204</v>
       </c>
       <c r="D1853">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1853" t="s">
         <v>206</v>
@@ -63747,7 +63747,7 @@
         <v>204</v>
       </c>
       <c r="D1854">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1854" t="s">
         <v>206</v>
@@ -63779,7 +63779,7 @@
         <v>204</v>
       </c>
       <c r="D1855">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1855" t="s">
         <v>206</v>
@@ -63811,7 +63811,7 @@
         <v>204</v>
       </c>
       <c r="D1856">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1856" t="s">
         <v>206</v>
@@ -63843,7 +63843,7 @@
         <v>204</v>
       </c>
       <c r="D1857">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1857" t="s">
         <v>206</v>
@@ -63875,7 +63875,7 @@
         <v>204</v>
       </c>
       <c r="D1858">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1858" t="s">
         <v>206</v>
@@ -63907,7 +63907,7 @@
         <v>204</v>
       </c>
       <c r="D1859">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1859" t="s">
         <v>206</v>
@@ -63939,7 +63939,7 @@
         <v>204</v>
       </c>
       <c r="D1860">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1860" t="s">
         <v>206</v>
@@ -63971,7 +63971,7 @@
         <v>204</v>
       </c>
       <c r="D1861">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1861" t="s">
         <v>206</v>
@@ -64003,7 +64003,7 @@
         <v>204</v>
       </c>
       <c r="D1862">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1862" t="s">
         <v>206</v>
@@ -64035,7 +64035,7 @@
         <v>204</v>
       </c>
       <c r="D1863">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1863" t="s">
         <v>206</v>
@@ -64070,7 +64070,7 @@
         <v>204</v>
       </c>
       <c r="D1864">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1864" t="s">
         <v>206</v>
@@ -64102,7 +64102,7 @@
         <v>204</v>
       </c>
       <c r="D1865">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1865" t="s">
         <v>206</v>
@@ -64134,7 +64134,7 @@
         <v>204</v>
       </c>
       <c r="D1866">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1866" t="s">
         <v>206</v>
@@ -64169,7 +64169,7 @@
         <v>204</v>
       </c>
       <c r="D1867">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1867" t="s">
         <v>206</v>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -88268,14 +88268,14 @@
         <v>8</v>
       </c>
       <c r="C28" s="8">
-        <v>46292</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>119</v>
+        <v>46299</v>
+      </c>
+      <c r="D28" t="s">
+        <v>17</v>
       </c>
       <c r="E28" t="str">
         <f t="shared" si="5"/>
-        <v>Baku City Circuit</v>
+        <v>Suzuka International Racing Course</v>
       </c>
       <c r="F28" t="s">
         <v>191</v>
@@ -88299,14 +88299,14 @@
         <v>9</v>
       </c>
       <c r="C29" s="8">
-        <v>46299</v>
-      </c>
-      <c r="D29" t="s">
-        <v>17</v>
+        <v>46306</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>166</v>
       </c>
       <c r="E29" t="str">
         <f t="shared" si="5"/>
-        <v>Suzuka International Racing Course</v>
+        <v>Marina Bay Street Circuit</v>
       </c>
       <c r="F29" t="s">
         <v>191</v>
@@ -88330,14 +88330,14 @@
         <v>10</v>
       </c>
       <c r="C30" s="8">
-        <v>46306</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>166</v>
+        <v>46313</v>
+      </c>
+      <c r="D30" t="s">
+        <v>120</v>
       </c>
       <c r="E30" t="str">
         <f t="shared" si="5"/>
-        <v>Marina Bay Street Circuit</v>
+        <v>Algarve International Circuit</v>
       </c>
       <c r="F30" t="s">
         <v>191</v>
@@ -88361,14 +88361,14 @@
         <v>11</v>
       </c>
       <c r="C31" s="8">
-        <v>46313</v>
-      </c>
-      <c r="D31" t="s">
-        <v>120</v>
+        <v>46320</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="E31" t="str">
         <f t="shared" ref="E31" si="6">VLOOKUP(D31,$K$1:$L$43,2,FALSE)</f>
-        <v>Algarve International Circuit</v>
+        <v>Circuit of the Americas</v>
       </c>
       <c r="F31" t="s">
         <v>191</v>
@@ -88392,14 +88392,14 @@
         <v>12</v>
       </c>
       <c r="C32" s="8">
-        <v>46320</v>
+        <v>46327</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="E32" t="str">
         <f t="shared" si="5"/>
-        <v>Circuit of the Americas</v>
+        <v>Autódromo Hermanos Rodríguez</v>
       </c>
       <c r="F32" t="s">
         <v>191</v>
@@ -88423,14 +88423,14 @@
         <v>13</v>
       </c>
       <c r="C33" s="8">
-        <v>46327</v>
+        <v>46334</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E33" t="str">
         <f t="shared" si="5"/>
-        <v>Autódromo Hermanos Rodríguez</v>
+        <v>Autódromo José Carlos Pace (Interlagos)</v>
       </c>
       <c r="F33" t="s">
         <v>191</v>
@@ -88454,14 +88454,14 @@
         <v>14</v>
       </c>
       <c r="C34" s="8">
-        <v>46334</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>171</v>
+        <v>46341</v>
+      </c>
+      <c r="D34" t="s">
+        <v>123</v>
       </c>
       <c r="E34" t="str">
         <f t="shared" si="5"/>
-        <v>Autódromo José Carlos Pace (Interlagos)</v>
+        <v>Red Bull Ring</v>
       </c>
       <c r="F34" t="s">
         <v>191</v>
@@ -88485,14 +88485,14 @@
         <v>15</v>
       </c>
       <c r="C35" s="8">
-        <v>46341</v>
-      </c>
-      <c r="D35" t="s">
-        <v>123</v>
+        <v>46348</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="E35" t="str">
         <f t="shared" si="5"/>
-        <v>Red Bull Ring</v>
+        <v>Las Vegas Strip Circuit</v>
       </c>
       <c r="F35" t="s">
         <v>191</v>
@@ -88510,14 +88510,14 @@
         <v>16</v>
       </c>
       <c r="C36" s="8">
-        <v>46348</v>
+        <v>46355</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E36" t="str">
         <f t="shared" si="5"/>
-        <v>Las Vegas Strip Circuit</v>
+        <v>Lusail International Circuit</v>
       </c>
       <c r="F36" t="s">
         <v>191</v>
@@ -88535,14 +88535,14 @@
         <v>17</v>
       </c>
       <c r="C37" s="8">
-        <v>46355</v>
+        <v>46362</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E37" t="str">
         <f t="shared" si="5"/>
-        <v>Lusail International Circuit</v>
+        <v>Yas Marina Circuit</v>
       </c>
       <c r="F37" t="s">
         <v>191</v>
@@ -88560,14 +88560,14 @@
         <v>18</v>
       </c>
       <c r="C38" s="8">
-        <v>46362</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>126</v>
+        <v>46369</v>
+      </c>
+      <c r="D38" t="s">
+        <v>125</v>
       </c>
       <c r="E38" t="str">
         <f t="shared" si="5"/>
-        <v>Yas Marina Circuit</v>
+        <v>Circuit Zandvoort</v>
       </c>
       <c r="F38" t="s">
         <v>191</v>
@@ -88585,14 +88585,14 @@
         <v>19</v>
       </c>
       <c r="C39" s="8">
-        <v>46369</v>
+        <v>46376</v>
       </c>
       <c r="D39" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="E39" t="str">
         <f t="shared" si="5"/>
-        <v>Circuit Zandvoort</v>
+        <v>Autodromo Nazionale Monza</v>
       </c>
       <c r="F39" t="s">
         <v>191</v>
@@ -88610,14 +88610,14 @@
         <v>20</v>
       </c>
       <c r="C40" s="8">
-        <v>46376</v>
+        <v>46383</v>
       </c>
       <c r="D40" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="E40" t="str">
         <f t="shared" si="5"/>
-        <v>Autodromo Nazionale Monza</v>
+        <v>Madring</v>
       </c>
       <c r="F40" t="s">
         <v>191</v>
@@ -88635,14 +88635,14 @@
         <v>21</v>
       </c>
       <c r="C41" s="8">
-        <v>46383</v>
+        <v>46390</v>
       </c>
       <c r="D41" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="E41" t="str">
         <f t="shared" si="5"/>
-        <v>Madring</v>
+        <v>Miami International Autodrome</v>
       </c>
       <c r="F41" t="s">
         <v>191</v>
@@ -88660,14 +88660,14 @@
         <v>22</v>
       </c>
       <c r="C42" s="8">
-        <v>46390</v>
-      </c>
-      <c r="D42" t="s">
-        <v>20</v>
+        <v>46397</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="E42" t="str">
         <f t="shared" ref="E42" si="7">VLOOKUP(D42,$K$1:$L$43,2,FALSE)</f>
-        <v>Miami International Autodrome</v>
+        <v>Baku City Circuit</v>
       </c>
       <c r="F42" t="s">
         <v>191</v>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -88677,12 +88677,54 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="C43" s="8"/>
-      <c r="G43" s="11"/>
+      <c r="A43" t="str">
+        <v>Teikirise</v>
+      </c>
+      <c r="B43" t="n">
+        <f>B42+1</f>
+        <v>23</v>
+      </c>
+      <c r="C43" t="n" s="8">
+        <v>46404</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Emilia Romagna GP</v>
+      </c>
+      <c r="E43" t="str">
+        <f>VLOOKUP(D43,$K$1:$L$43,2,FALSE)</f>
+        <v>Autodromo Enzo e Dino Ferrari (Imola)</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Upcoming</v>
+      </c>
+      <c r="G43" t="n" s="11">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="C44" s="8"/>
-      <c r="G44" s="11"/>
+      <c r="A44" t="str">
+        <v>Teikirise</v>
+      </c>
+      <c r="B44" t="n">
+        <f>B43+1</f>
+        <v>24</v>
+      </c>
+      <c r="C44" t="n" s="8">
+        <v>46411</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Bahrain GP</v>
+      </c>
+      <c r="E44" t="str">
+        <f>VLOOKUP(D44,$K$1:$L$43,2,FALSE)</f>
+        <v>Bahrain International Circuit</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Upcoming</v>
+      </c>
+      <c r="G44" t="n" s="11">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C45" s="8"/>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -64194,179 +64194,1235 @@
       </c>
     </row>
     <row r="1868" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="F1868" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1868" t="s">
-        <v>37</v>
+      <c r="A1868" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1868" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1868" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1868">
+        <v>8</v>
+      </c>
+      <c r="E1868" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1868" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1868" t="inlineStr">
+        <is>
+          <t>TomasRodri21</t>
+        </is>
+      </c>
+      <c r="H1868" t="inlineStr">
+        <is>
+          <t>McLaren</t>
+        </is>
+      </c>
+      <c r="I1868">
+        <v>1</v>
+      </c>
+      <c r="J1868">
+        <v>25</v>
+      </c>
+      <c r="K1868" t="inlineStr">
+        <is>
+          <t>88:56.869</t>
+        </is>
+      </c>
+      <c r="L1868" t="inlineStr">
+        <is>
+          <t>1:33.169</t>
+        </is>
       </c>
     </row>
     <row r="1869" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="F1869" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1869" t="s">
-        <v>37</v>
+      <c r="A1869" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1869" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1869" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1869">
+        <v>8</v>
+      </c>
+      <c r="E1869" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1869" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1869" t="inlineStr">
+        <is>
+          <t>Fatacuida</t>
+        </is>
+      </c>
+      <c r="H1869" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="I1869">
+        <v>2</v>
+      </c>
+      <c r="J1869">
+        <v>18</v>
+      </c>
+      <c r="K1869" t="inlineStr">
+        <is>
+          <t>+11.242</t>
+        </is>
+      </c>
+      <c r="L1869" t="inlineStr">
+        <is>
+          <t>1:34.042</t>
+        </is>
       </c>
     </row>
     <row r="1870" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="F1870" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1870" t="s">
-        <v>37</v>
+      <c r="A1870" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1870" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1870" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1870">
+        <v>8</v>
+      </c>
+      <c r="E1870" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1870" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1870" t="inlineStr">
+        <is>
+          <t>Max Verstappen</t>
+        </is>
+      </c>
+      <c r="H1870" t="inlineStr">
+        <is>
+          <t>Red Bull</t>
+        </is>
+      </c>
+      <c r="I1870">
+        <v>3</v>
+      </c>
+      <c r="J1870">
+        <v>15</v>
+      </c>
+      <c r="K1870" t="inlineStr">
+        <is>
+          <t>+18.485</t>
+        </is>
+      </c>
+      <c r="L1870" t="inlineStr">
+        <is>
+          <t>1:35.476</t>
+        </is>
       </c>
     </row>
     <row r="1871" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="F1871" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1871" t="s">
-        <v>37</v>
+      <c r="A1871" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1871" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1871" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1871">
+        <v>8</v>
+      </c>
+      <c r="E1871" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1871" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1871" t="inlineStr">
+        <is>
+          <t>Charles Leclerc</t>
+        </is>
+      </c>
+      <c r="H1871" t="inlineStr">
+        <is>
+          <t>Ferrari</t>
+        </is>
+      </c>
+      <c r="I1871">
+        <v>4</v>
+      </c>
+      <c r="J1871">
+        <v>12</v>
+      </c>
+      <c r="K1871" t="inlineStr">
+        <is>
+          <t>+24.428</t>
+        </is>
+      </c>
+      <c r="L1871" t="inlineStr">
+        <is>
+          <t>1:35.329</t>
+        </is>
       </c>
     </row>
     <row r="1872" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="F1872" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1872" t="s">
-        <v>37</v>
+      <c r="A1872" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1872" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1872">
+        <v>8</v>
+      </c>
+      <c r="E1872" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1872" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1872" t="inlineStr">
+        <is>
+          <t>Carlos Sainz Jr.</t>
+        </is>
+      </c>
+      <c r="H1872" t="inlineStr">
+        <is>
+          <t>Williams</t>
+        </is>
+      </c>
+      <c r="I1872">
+        <v>5</v>
+      </c>
+      <c r="J1872">
+        <v>10</v>
+      </c>
+      <c r="K1872" t="inlineStr">
+        <is>
+          <t>+29.581</t>
+        </is>
+      </c>
+      <c r="L1872" t="inlineStr">
+        <is>
+          <t>1:35.906</t>
+        </is>
       </c>
     </row>
     <row r="1873" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1873" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1873" t="s">
-        <v>37</v>
+      <c r="A1873" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1873" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1873" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1873">
+        <v>8</v>
+      </c>
+      <c r="E1873" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1873" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1873" t="inlineStr">
+        <is>
+          <t>Alexander Albon</t>
+        </is>
+      </c>
+      <c r="H1873" t="inlineStr">
+        <is>
+          <t>Williams</t>
+        </is>
+      </c>
+      <c r="I1873">
+        <v>6</v>
+      </c>
+      <c r="J1873">
+        <v>8</v>
+      </c>
+      <c r="K1873" t="inlineStr">
+        <is>
+          <t>+31.063</t>
+        </is>
+      </c>
+      <c r="L1873" t="inlineStr">
+        <is>
+          <t>1:36.226</t>
+        </is>
       </c>
     </row>
     <row r="1874" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1874" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1874" t="s">
-        <v>37</v>
+      <c r="A1874" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1874" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1874" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1874">
+        <v>8</v>
+      </c>
+      <c r="E1874" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1874" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1874" t="inlineStr">
+        <is>
+          <t>Lewis Hamilton</t>
+        </is>
+      </c>
+      <c r="H1874" t="inlineStr">
+        <is>
+          <t>Ferrari</t>
+        </is>
+      </c>
+      <c r="I1874">
+        <v>7</v>
+      </c>
+      <c r="J1874">
+        <v>6</v>
+      </c>
+      <c r="K1874" t="inlineStr">
+        <is>
+          <t>+39.035</t>
+        </is>
+      </c>
+      <c r="L1874" t="inlineStr">
+        <is>
+          <t>1:37.026</t>
+        </is>
       </c>
     </row>
     <row r="1875" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1875" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1875" t="s">
-        <v>37</v>
+      <c r="A1875" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1875" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1875" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1875">
+        <v>8</v>
+      </c>
+      <c r="E1875" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1875" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1875" t="inlineStr">
+        <is>
+          <t>Fernando Alonso</t>
+        </is>
+      </c>
+      <c r="H1875" t="inlineStr">
+        <is>
+          <t>Aston Martin</t>
+        </is>
+      </c>
+      <c r="I1875">
+        <v>8</v>
+      </c>
+      <c r="J1875">
+        <v>4</v>
+      </c>
+      <c r="K1875" t="inlineStr">
+        <is>
+          <t>+39.430</t>
+        </is>
+      </c>
+      <c r="L1875" t="inlineStr">
+        <is>
+          <t>1:36.685</t>
+        </is>
       </c>
     </row>
     <row r="1876" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1876" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1876" t="s">
-        <v>37</v>
+      <c r="A1876" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1876" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1876" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1876">
+        <v>8</v>
+      </c>
+      <c r="E1876" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1876" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1876" t="inlineStr">
+        <is>
+          <t>Franco Colapinto</t>
+        </is>
+      </c>
+      <c r="H1876" t="inlineStr">
+        <is>
+          <t>Alpine</t>
+        </is>
+      </c>
+      <c r="I1876">
+        <v>9</v>
+      </c>
+      <c r="J1876">
+        <v>2</v>
+      </c>
+      <c r="K1876" t="inlineStr">
+        <is>
+          <t>+44.676</t>
+        </is>
+      </c>
+      <c r="L1876" t="inlineStr">
+        <is>
+          <t>1:37.128</t>
+        </is>
       </c>
     </row>
     <row r="1877" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1877" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1877" t="s">
-        <v>37</v>
+      <c r="A1877" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1877" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1877">
+        <v>8</v>
+      </c>
+      <c r="E1877" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1877" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1877" t="inlineStr">
+        <is>
+          <t>Kimi Antonelli</t>
+        </is>
+      </c>
+      <c r="H1877" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="I1877">
+        <v>10</v>
+      </c>
+      <c r="J1877">
+        <v>1</v>
+      </c>
+      <c r="K1877" t="inlineStr">
+        <is>
+          <t>+44.869</t>
+        </is>
+      </c>
+      <c r="L1877" t="inlineStr">
+        <is>
+          <t>1:37.212</t>
+        </is>
       </c>
     </row>
     <row r="1878" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1878" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1878" t="s">
-        <v>37</v>
+      <c r="A1878" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1878" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1878">
+        <v>8</v>
+      </c>
+      <c r="E1878" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1878" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1878" t="inlineStr">
+        <is>
+          <t>Arvid Lidblad</t>
+        </is>
+      </c>
+      <c r="H1878" t="inlineStr">
+        <is>
+          <t>Racing Bulls</t>
+        </is>
+      </c>
+      <c r="I1878">
+        <v>11</v>
+      </c>
+      <c r="J1878">
+        <v>0</v>
+      </c>
+      <c r="K1878" t="inlineStr">
+        <is>
+          <t>+44.934</t>
+        </is>
+      </c>
+      <c r="L1878" t="inlineStr">
+        <is>
+          <t>1:37.293</t>
+        </is>
       </c>
     </row>
     <row r="1879" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1879" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1879" t="s">
-        <v>37</v>
+      <c r="A1879" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1879" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1879">
+        <v>8</v>
+      </c>
+      <c r="E1879" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1879" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1879" t="inlineStr">
+        <is>
+          <t>Liam Lawson</t>
+        </is>
+      </c>
+      <c r="H1879" t="inlineStr">
+        <is>
+          <t>Racing Bulls</t>
+        </is>
+      </c>
+      <c r="I1879">
+        <v>12</v>
+      </c>
+      <c r="J1879">
+        <v>0</v>
+      </c>
+      <c r="K1879" t="inlineStr">
+        <is>
+          <t>+46.047</t>
+        </is>
+      </c>
+      <c r="L1879" t="inlineStr">
+        <is>
+          <t>1:37.178</t>
+        </is>
       </c>
     </row>
     <row r="1880" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1880" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1880" t="s">
-        <v>37</v>
+      <c r="A1880" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1880" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1880">
+        <v>8</v>
+      </c>
+      <c r="E1880" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1880" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1880" t="inlineStr">
+        <is>
+          <t>Oliver Bearman</t>
+        </is>
+      </c>
+      <c r="H1880" t="inlineStr">
+        <is>
+          <t>Haas</t>
+        </is>
+      </c>
+      <c r="I1880">
+        <v>13</v>
+      </c>
+      <c r="J1880">
+        <v>0</v>
+      </c>
+      <c r="K1880" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1880" t="inlineStr">
+        <is>
+          <t>1:36.028</t>
+        </is>
       </c>
     </row>
     <row r="1881" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1881" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1881" t="s">
-        <v>37</v>
+      <c r="A1881" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1881" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1881">
+        <v>8</v>
+      </c>
+      <c r="E1881" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1881" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1881" t="inlineStr">
+        <is>
+          <t>Esteban Ocon</t>
+        </is>
+      </c>
+      <c r="H1881" t="inlineStr">
+        <is>
+          <t>Haas</t>
+        </is>
+      </c>
+      <c r="I1881">
+        <v>14</v>
+      </c>
+      <c r="J1881">
+        <v>0</v>
+      </c>
+      <c r="K1881" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1881" t="inlineStr">
+        <is>
+          <t>1:35.840</t>
+        </is>
       </c>
     </row>
     <row r="1882" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1882" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1882" t="s">
-        <v>37</v>
+      <c r="A1882" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1882" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1882">
+        <v>8</v>
+      </c>
+      <c r="E1882" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1882" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1882" t="inlineStr">
+        <is>
+          <t>Nico Hülkenberg</t>
+        </is>
+      </c>
+      <c r="H1882" t="inlineStr">
+        <is>
+          <t>Audi</t>
+        </is>
+      </c>
+      <c r="I1882">
+        <v>15</v>
+      </c>
+      <c r="J1882">
+        <v>0</v>
+      </c>
+      <c r="K1882" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1882" t="inlineStr">
+        <is>
+          <t>1:37.347</t>
+        </is>
       </c>
     </row>
     <row r="1883" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1883" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1883" t="s">
-        <v>37</v>
+      <c r="A1883" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1883" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1883">
+        <v>8</v>
+      </c>
+      <c r="E1883" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1883" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1883" t="inlineStr">
+        <is>
+          <t>Valtteri Bottas</t>
+        </is>
+      </c>
+      <c r="H1883" t="inlineStr">
+        <is>
+          <t>Cadillac</t>
+        </is>
+      </c>
+      <c r="I1883">
+        <v>16</v>
+      </c>
+      <c r="J1883">
+        <v>0</v>
+      </c>
+      <c r="K1883" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1883" t="inlineStr">
+        <is>
+          <t>1:37.179</t>
+        </is>
       </c>
     </row>
     <row r="1884" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1884" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1884" t="s">
-        <v>37</v>
+      <c r="A1884" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1884" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1884">
+        <v>8</v>
+      </c>
+      <c r="E1884" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1884" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1884" t="inlineStr">
+        <is>
+          <t>Lance Stroll</t>
+        </is>
+      </c>
+      <c r="H1884" t="inlineStr">
+        <is>
+          <t>Aston Martin</t>
+        </is>
+      </c>
+      <c r="I1884">
+        <v>17</v>
+      </c>
+      <c r="J1884">
+        <v>0</v>
+      </c>
+      <c r="K1884" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1884" t="inlineStr">
+        <is>
+          <t>1:37.916</t>
+        </is>
       </c>
     </row>
     <row r="1885" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1885" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1885" t="s">
-        <v>37</v>
+      <c r="A1885" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1885" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1885">
+        <v>8</v>
+      </c>
+      <c r="E1885" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1885" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1885" t="inlineStr">
+        <is>
+          <t>Gabriel Bortoleto</t>
+        </is>
+      </c>
+      <c r="H1885" t="inlineStr">
+        <is>
+          <t>Audi</t>
+        </is>
+      </c>
+      <c r="I1885">
+        <v>18</v>
+      </c>
+      <c r="J1885">
+        <v>0</v>
+      </c>
+      <c r="K1885" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1885" t="inlineStr">
+        <is>
+          <t>1:37.930</t>
+        </is>
       </c>
     </row>
     <row r="1886" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1886" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1886" t="s">
-        <v>37</v>
+      <c r="A1886" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1886" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1886">
+        <v>8</v>
+      </c>
+      <c r="E1886" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1886" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1886" t="inlineStr">
+        <is>
+          <t>Sergio Perez</t>
+        </is>
+      </c>
+      <c r="H1886" t="inlineStr">
+        <is>
+          <t>Cadillac</t>
+        </is>
+      </c>
+      <c r="I1886">
+        <v>19</v>
+      </c>
+      <c r="J1886">
+        <v>0</v>
+      </c>
+      <c r="K1886" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1886" t="inlineStr">
+        <is>
+          <t>1:39.014</t>
+        </is>
       </c>
     </row>
     <row r="1887" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1887" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1887" t="s">
-        <v>37</v>
+      <c r="A1887" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1887" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1887" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1887">
+        <v>8</v>
+      </c>
+      <c r="E1887" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1887" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1887" t="inlineStr">
+        <is>
+          <t>Polingua</t>
+        </is>
+      </c>
+      <c r="H1887" t="inlineStr">
+        <is>
+          <t>Red Bull</t>
+        </is>
+      </c>
+      <c r="I1887">
+        <v>20</v>
+      </c>
+      <c r="J1887">
+        <v>0</v>
+      </c>
+      <c r="K1887" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+      <c r="L1887" t="inlineStr">
+        <is>
+          <t>1:36.147</t>
+        </is>
       </c>
     </row>
     <row r="1888" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1888" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1888" t="s">
-        <v>37</v>
+      <c r="A1888" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1888" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1888" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1888">
+        <v>8</v>
+      </c>
+      <c r="E1888" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1888" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1888" t="inlineStr">
+        <is>
+          <t>Lando Norris</t>
+        </is>
+      </c>
+      <c r="H1888" t="inlineStr">
+        <is>
+          <t>McLaren</t>
+        </is>
+      </c>
+      <c r="I1888">
+        <v>21</v>
+      </c>
+      <c r="J1888">
+        <v>0</v>
+      </c>
+      <c r="K1888" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+      <c r="L1888" t="inlineStr">
+        <is>
+          <t>1:35.788</t>
+        </is>
       </c>
     </row>
     <row r="1889" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1889" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1889" t="s">
-        <v>37</v>
+      <c r="A1889" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1889" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1889" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1889">
+        <v>8</v>
+      </c>
+      <c r="E1889" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1889" t="inlineStr">
+        <is>
+          <t>Japanese GP</t>
+        </is>
+      </c>
+      <c r="G1889" t="inlineStr">
+        <is>
+          <t>Pierre Gasly</t>
+        </is>
+      </c>
+      <c r="H1889" t="inlineStr">
+        <is>
+          <t>Alpine</t>
+        </is>
+      </c>
+      <c r="I1889">
+        <v>22</v>
+      </c>
+      <c r="J1889">
+        <v>0</v>
+      </c>
+      <c r="K1889" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+      <c r="L1889" t="inlineStr">
+        <is>
+          <t>1:37.326</t>
+        </is>
       </c>
     </row>
     <row r="1890" spans="6:10" x14ac:dyDescent="0.45">
@@ -88277,8 +89333,10 @@
         <f t="shared" si="5"/>
         <v>Suzuka International Racing Course</v>
       </c>
-      <c r="F28" t="s">
-        <v>191</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="G28" s="11">
         <v>0.25</v>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ruiro\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8606141A-2CDE-4C30-951C-61039481B922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE8B375-D277-4CB3-99D4-0570098D3F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Leagues" sheetId="10" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19588" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19748" uniqueCount="500">
   <si>
     <t>Lewis Hamilton</t>
   </si>
@@ -1456,6 +1456,108 @@
   <si>
     <t>Retired</t>
   </si>
+  <si>
+    <t>88:56.869</t>
+  </si>
+  <si>
+    <t>1:33.169</t>
+  </si>
+  <si>
+    <t>+11.242</t>
+  </si>
+  <si>
+    <t>1:34.042</t>
+  </si>
+  <si>
+    <t>+18.485</t>
+  </si>
+  <si>
+    <t>1:35.476</t>
+  </si>
+  <si>
+    <t>+24.428</t>
+  </si>
+  <si>
+    <t>1:35.329</t>
+  </si>
+  <si>
+    <t>+29.581</t>
+  </si>
+  <si>
+    <t>1:35.906</t>
+  </si>
+  <si>
+    <t>+31.063</t>
+  </si>
+  <si>
+    <t>1:36.226</t>
+  </si>
+  <si>
+    <t>+39.035</t>
+  </si>
+  <si>
+    <t>1:37.026</t>
+  </si>
+  <si>
+    <t>+39.430</t>
+  </si>
+  <si>
+    <t>1:36.685</t>
+  </si>
+  <si>
+    <t>+44.676</t>
+  </si>
+  <si>
+    <t>1:37.128</t>
+  </si>
+  <si>
+    <t>+44.869</t>
+  </si>
+  <si>
+    <t>1:37.212</t>
+  </si>
+  <si>
+    <t>+44.934</t>
+  </si>
+  <si>
+    <t>1:37.293</t>
+  </si>
+  <si>
+    <t>+46.047</t>
+  </si>
+  <si>
+    <t>1:37.178</t>
+  </si>
+  <si>
+    <t>1:36.028</t>
+  </si>
+  <si>
+    <t>1:35.840</t>
+  </si>
+  <si>
+    <t>1:37.347</t>
+  </si>
+  <si>
+    <t>1:37.179</t>
+  </si>
+  <si>
+    <t>1:37.916</t>
+  </si>
+  <si>
+    <t>1:37.930</t>
+  </si>
+  <si>
+    <t>1:39.014</t>
+  </si>
+  <si>
+    <t>1:36.147</t>
+  </si>
+  <si>
+    <t>1:35.788</t>
+  </si>
+  <si>
+    <t>1:37.326</t>
+  </si>
 </sst>
 </file>
 
@@ -63832,7 +63934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1857" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1857" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1857" t="s">
         <v>197</v>
       </c>
@@ -63864,7 +63966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1858" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1858" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1858" t="s">
         <v>197</v>
       </c>
@@ -63896,7 +63998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1859" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1859" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1859" t="s">
         <v>197</v>
       </c>
@@ -63928,7 +64030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1860" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1860" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1860" t="s">
         <v>197</v>
       </c>
@@ -63960,7 +64062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1861" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1861" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1861" t="s">
         <v>197</v>
       </c>
@@ -63992,7 +64094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1862" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1862" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1862" t="s">
         <v>197</v>
       </c>
@@ -64024,7 +64126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1863" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1863" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1863" t="s">
         <v>197</v>
       </c>
@@ -64059,7 +64161,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="1864" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1864" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1864" t="s">
         <v>197</v>
       </c>
@@ -64091,7 +64193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1865" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1865" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1865" t="s">
         <v>197</v>
       </c>
@@ -64123,7 +64225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1866" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1866" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1866" t="s">
         <v>197</v>
       </c>
@@ -64158,7 +64260,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="1867" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1867" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1867" t="s">
         <v>197</v>
       </c>
@@ -64193,44 +64295,30 @@
         <v>194</v>
       </c>
     </row>
-    <row r="1868" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A1868" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1868" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1868" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+    <row r="1868" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1868" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1868" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1868" t="s">
+        <v>204</v>
       </c>
       <c r="D1868">
         <v>8</v>
       </c>
-      <c r="E1868" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1868" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1868" t="inlineStr">
-        <is>
-          <t>TomasRodri21</t>
-        </is>
-      </c>
-      <c r="H1868" t="inlineStr">
-        <is>
-          <t>McLaren</t>
-        </is>
+      <c r="E1868" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1868" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1868" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1868" t="s">
+        <v>143</v>
       </c>
       <c r="I1868">
         <v>1</v>
@@ -64238,55 +64326,37 @@
       <c r="J1868">
         <v>25</v>
       </c>
-      <c r="K1868" t="inlineStr">
-        <is>
-          <t>88:56.869</t>
-        </is>
-      </c>
-      <c r="L1868" t="inlineStr">
-        <is>
-          <t>1:33.169</t>
-        </is>
-      </c>
-    </row>
-    <row r="1869" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A1869" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1869" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1869" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1868" t="s">
+        <v>466</v>
+      </c>
+      <c r="L1868" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1869" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1869" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1869" t="s">
+        <v>204</v>
       </c>
       <c r="D1869">
         <v>8</v>
       </c>
-      <c r="E1869" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1869" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1869" t="inlineStr">
-        <is>
-          <t>Fatacuida</t>
-        </is>
-      </c>
-      <c r="H1869" t="inlineStr">
-        <is>
-          <t>Mercedes</t>
-        </is>
+      <c r="E1869" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1869" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1869" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1869" t="s">
+        <v>134</v>
       </c>
       <c r="I1869">
         <v>2</v>
@@ -64294,55 +64364,37 @@
       <c r="J1869">
         <v>18</v>
       </c>
-      <c r="K1869" t="inlineStr">
-        <is>
-          <t>+11.242</t>
-        </is>
-      </c>
-      <c r="L1869" t="inlineStr">
-        <is>
-          <t>1:34.042</t>
-        </is>
-      </c>
-    </row>
-    <row r="1870" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A1870" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1870" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1870" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1869" t="s">
+        <v>468</v>
+      </c>
+      <c r="L1869" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1870" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1870" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1870" t="s">
+        <v>204</v>
       </c>
       <c r="D1870">
         <v>8</v>
       </c>
-      <c r="E1870" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1870" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1870" t="inlineStr">
-        <is>
-          <t>Max Verstappen</t>
-        </is>
-      </c>
-      <c r="H1870" t="inlineStr">
-        <is>
-          <t>Red Bull</t>
-        </is>
+      <c r="E1870" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1870" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1870" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1870" t="s">
+        <v>135</v>
       </c>
       <c r="I1870">
         <v>3</v>
@@ -64350,55 +64402,37 @@
       <c r="J1870">
         <v>15</v>
       </c>
-      <c r="K1870" t="inlineStr">
-        <is>
-          <t>+18.485</t>
-        </is>
-      </c>
-      <c r="L1870" t="inlineStr">
-        <is>
-          <t>1:35.476</t>
-        </is>
-      </c>
-    </row>
-    <row r="1871" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A1871" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1871" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1871" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1870" t="s">
+        <v>470</v>
+      </c>
+      <c r="L1870" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1871" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1871" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1871" t="s">
+        <v>204</v>
       </c>
       <c r="D1871">
         <v>8</v>
       </c>
-      <c r="E1871" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1871" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1871" t="inlineStr">
-        <is>
-          <t>Charles Leclerc</t>
-        </is>
-      </c>
-      <c r="H1871" t="inlineStr">
-        <is>
-          <t>Ferrari</t>
-        </is>
+      <c r="E1871" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1871" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1871" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1871" t="s">
+        <v>138</v>
       </c>
       <c r="I1871">
         <v>4</v>
@@ -64406,55 +64440,37 @@
       <c r="J1871">
         <v>12</v>
       </c>
-      <c r="K1871" t="inlineStr">
-        <is>
-          <t>+24.428</t>
-        </is>
-      </c>
-      <c r="L1871" t="inlineStr">
-        <is>
-          <t>1:35.329</t>
-        </is>
-      </c>
-    </row>
-    <row r="1872" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A1872" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1872" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1872" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1871" t="s">
+        <v>472</v>
+      </c>
+      <c r="L1871" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1872" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1872" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1872" t="s">
+        <v>204</v>
       </c>
       <c r="D1872">
         <v>8</v>
       </c>
-      <c r="E1872" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1872" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1872" t="inlineStr">
-        <is>
-          <t>Carlos Sainz Jr.</t>
-        </is>
-      </c>
-      <c r="H1872" t="inlineStr">
-        <is>
-          <t>Williams</t>
-        </is>
+      <c r="E1872" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1872" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1872" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1872" t="s">
+        <v>139</v>
       </c>
       <c r="I1872">
         <v>5</v>
@@ -64462,55 +64478,37 @@
       <c r="J1872">
         <v>10</v>
       </c>
-      <c r="K1872" t="inlineStr">
-        <is>
-          <t>+29.581</t>
-        </is>
-      </c>
-      <c r="L1872" t="inlineStr">
-        <is>
-          <t>1:35.906</t>
-        </is>
-      </c>
-    </row>
-    <row r="1873" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1873" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1873" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1873" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1872" t="s">
+        <v>474</v>
+      </c>
+      <c r="L1872" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1873" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1873" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1873" t="s">
+        <v>204</v>
       </c>
       <c r="D1873">
         <v>8</v>
       </c>
-      <c r="E1873" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1873" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1873" t="inlineStr">
-        <is>
-          <t>Alexander Albon</t>
-        </is>
-      </c>
-      <c r="H1873" t="inlineStr">
-        <is>
-          <t>Williams</t>
-        </is>
+      <c r="E1873" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1873" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1873" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1873" t="s">
+        <v>139</v>
       </c>
       <c r="I1873">
         <v>6</v>
@@ -64518,55 +64516,37 @@
       <c r="J1873">
         <v>8</v>
       </c>
-      <c r="K1873" t="inlineStr">
-        <is>
-          <t>+31.063</t>
-        </is>
-      </c>
-      <c r="L1873" t="inlineStr">
-        <is>
-          <t>1:36.226</t>
-        </is>
-      </c>
-    </row>
-    <row r="1874" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1874" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1874" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1874" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1873" t="s">
+        <v>476</v>
+      </c>
+      <c r="L1873" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1874" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1874" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1874" t="s">
+        <v>204</v>
       </c>
       <c r="D1874">
         <v>8</v>
       </c>
-      <c r="E1874" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1874" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1874" t="inlineStr">
-        <is>
-          <t>Lewis Hamilton</t>
-        </is>
-      </c>
-      <c r="H1874" t="inlineStr">
-        <is>
-          <t>Ferrari</t>
-        </is>
+      <c r="E1874" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1874" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1874" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1874" t="s">
+        <v>138</v>
       </c>
       <c r="I1874">
         <v>7</v>
@@ -64574,55 +64554,37 @@
       <c r="J1874">
         <v>6</v>
       </c>
-      <c r="K1874" t="inlineStr">
-        <is>
-          <t>+39.035</t>
-        </is>
-      </c>
-      <c r="L1874" t="inlineStr">
-        <is>
-          <t>1:37.026</t>
-        </is>
-      </c>
-    </row>
-    <row r="1875" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1875" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1875" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1875" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1874" t="s">
+        <v>478</v>
+      </c>
+      <c r="L1874" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1875" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1875" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1875" t="s">
+        <v>204</v>
       </c>
       <c r="D1875">
         <v>8</v>
       </c>
-      <c r="E1875" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1875" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1875" t="inlineStr">
-        <is>
-          <t>Fernando Alonso</t>
-        </is>
-      </c>
-      <c r="H1875" t="inlineStr">
-        <is>
-          <t>Aston Martin</t>
-        </is>
+      <c r="E1875" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1875" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1875" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1875" t="s">
+        <v>133</v>
       </c>
       <c r="I1875">
         <v>8</v>
@@ -64630,55 +64592,37 @@
       <c r="J1875">
         <v>4</v>
       </c>
-      <c r="K1875" t="inlineStr">
-        <is>
-          <t>+39.430</t>
-        </is>
-      </c>
-      <c r="L1875" t="inlineStr">
-        <is>
-          <t>1:36.685</t>
-        </is>
-      </c>
-    </row>
-    <row r="1876" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1876" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1876" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1876" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1875" t="s">
+        <v>480</v>
+      </c>
+      <c r="L1875" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1876" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1876" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1876" t="s">
+        <v>204</v>
       </c>
       <c r="D1876">
         <v>8</v>
       </c>
-      <c r="E1876" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1876" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1876" t="inlineStr">
-        <is>
-          <t>Franco Colapinto</t>
-        </is>
-      </c>
-      <c r="H1876" t="inlineStr">
-        <is>
-          <t>Alpine</t>
-        </is>
+      <c r="E1876" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1876" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1876" t="s">
+        <v>201</v>
+      </c>
+      <c r="H1876" t="s">
+        <v>140</v>
       </c>
       <c r="I1876">
         <v>9</v>
@@ -64686,55 +64630,37 @@
       <c r="J1876">
         <v>2</v>
       </c>
-      <c r="K1876" t="inlineStr">
-        <is>
-          <t>+44.676</t>
-        </is>
-      </c>
-      <c r="L1876" t="inlineStr">
-        <is>
-          <t>1:37.128</t>
-        </is>
-      </c>
-    </row>
-    <row r="1877" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1877" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1877" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1877" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1876" t="s">
+        <v>482</v>
+      </c>
+      <c r="L1876" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1877" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1877" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1877" t="s">
+        <v>204</v>
       </c>
       <c r="D1877">
         <v>8</v>
       </c>
-      <c r="E1877" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1877" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1877" t="inlineStr">
-        <is>
-          <t>Kimi Antonelli</t>
-        </is>
-      </c>
-      <c r="H1877" t="inlineStr">
-        <is>
-          <t>Mercedes</t>
-        </is>
+      <c r="E1877" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1877" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1877" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1877" t="s">
+        <v>134</v>
       </c>
       <c r="I1877">
         <v>10</v>
@@ -64742,55 +64668,37 @@
       <c r="J1877">
         <v>1</v>
       </c>
-      <c r="K1877" t="inlineStr">
-        <is>
-          <t>+44.869</t>
-        </is>
-      </c>
-      <c r="L1877" t="inlineStr">
-        <is>
-          <t>1:37.212</t>
-        </is>
-      </c>
-    </row>
-    <row r="1878" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1878" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1878" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1878" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1877" t="s">
+        <v>484</v>
+      </c>
+      <c r="L1877" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1878" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1878" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1878" t="s">
+        <v>204</v>
       </c>
       <c r="D1878">
         <v>8</v>
       </c>
-      <c r="E1878" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1878" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1878" t="inlineStr">
-        <is>
-          <t>Arvid Lidblad</t>
-        </is>
-      </c>
-      <c r="H1878" t="inlineStr">
-        <is>
-          <t>Racing Bulls</t>
-        </is>
+      <c r="E1878" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1878" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1878" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1878" t="s">
+        <v>144</v>
       </c>
       <c r="I1878">
         <v>11</v>
@@ -64798,55 +64706,37 @@
       <c r="J1878">
         <v>0</v>
       </c>
-      <c r="K1878" t="inlineStr">
-        <is>
-          <t>+44.934</t>
-        </is>
-      </c>
-      <c r="L1878" t="inlineStr">
-        <is>
-          <t>1:37.293</t>
-        </is>
-      </c>
-    </row>
-    <row r="1879" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1879" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1879" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1879" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1878" t="s">
+        <v>486</v>
+      </c>
+      <c r="L1878" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1879" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1879" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1879" t="s">
+        <v>204</v>
       </c>
       <c r="D1879">
         <v>8</v>
       </c>
-      <c r="E1879" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1879" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1879" t="inlineStr">
-        <is>
-          <t>Liam Lawson</t>
-        </is>
-      </c>
-      <c r="H1879" t="inlineStr">
-        <is>
-          <t>Racing Bulls</t>
-        </is>
+      <c r="E1879" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1879" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1879" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1879" t="s">
+        <v>144</v>
       </c>
       <c r="I1879">
         <v>12</v>
@@ -64854,55 +64744,37 @@
       <c r="J1879">
         <v>0</v>
       </c>
-      <c r="K1879" t="inlineStr">
-        <is>
-          <t>+46.047</t>
-        </is>
-      </c>
-      <c r="L1879" t="inlineStr">
-        <is>
-          <t>1:37.178</t>
-        </is>
-      </c>
-    </row>
-    <row r="1880" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1880" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1880" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1880" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1879" t="s">
+        <v>488</v>
+      </c>
+      <c r="L1879" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1880" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1880" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1880" t="s">
+        <v>204</v>
       </c>
       <c r="D1880">
         <v>8</v>
       </c>
-      <c r="E1880" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1880" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1880" t="inlineStr">
-        <is>
-          <t>Oliver Bearman</t>
-        </is>
-      </c>
-      <c r="H1880" t="inlineStr">
-        <is>
-          <t>Haas</t>
-        </is>
+      <c r="E1880" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1880" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1880" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1880" t="s">
+        <v>137</v>
       </c>
       <c r="I1880">
         <v>13</v>
@@ -64910,55 +64782,37 @@
       <c r="J1880">
         <v>0</v>
       </c>
-      <c r="K1880" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1880" t="inlineStr">
-        <is>
-          <t>1:36.028</t>
-        </is>
-      </c>
-    </row>
-    <row r="1881" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1881" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1881" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1881" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1880" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1880" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1881" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1881" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1881" t="s">
+        <v>204</v>
       </c>
       <c r="D1881">
         <v>8</v>
       </c>
-      <c r="E1881" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1881" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1881" t="inlineStr">
-        <is>
-          <t>Esteban Ocon</t>
-        </is>
-      </c>
-      <c r="H1881" t="inlineStr">
-        <is>
-          <t>Haas</t>
-        </is>
+      <c r="E1881" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1881" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1881" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1881" t="s">
+        <v>137</v>
       </c>
       <c r="I1881">
         <v>14</v>
@@ -64966,55 +64820,37 @@
       <c r="J1881">
         <v>0</v>
       </c>
-      <c r="K1881" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1881" t="inlineStr">
-        <is>
-          <t>1:35.840</t>
-        </is>
-      </c>
-    </row>
-    <row r="1882" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1882" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1882" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1882" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1881" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1881" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1882" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1882" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1882" t="s">
+        <v>204</v>
       </c>
       <c r="D1882">
         <v>8</v>
       </c>
-      <c r="E1882" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1882" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1882" t="inlineStr">
-        <is>
-          <t>Nico Hülkenberg</t>
-        </is>
-      </c>
-      <c r="H1882" t="inlineStr">
-        <is>
-          <t>Audi</t>
-        </is>
+      <c r="E1882" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1882" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1882" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1882" t="s">
+        <v>198</v>
       </c>
       <c r="I1882">
         <v>15</v>
@@ -65022,55 +64858,37 @@
       <c r="J1882">
         <v>0</v>
       </c>
-      <c r="K1882" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1882" t="inlineStr">
-        <is>
-          <t>1:37.347</t>
-        </is>
-      </c>
-    </row>
-    <row r="1883" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1883" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1883" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1883" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1882" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1882" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1883" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1883" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1883" t="s">
+        <v>204</v>
       </c>
       <c r="D1883">
         <v>8</v>
       </c>
-      <c r="E1883" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1883" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1883" t="inlineStr">
-        <is>
-          <t>Valtteri Bottas</t>
-        </is>
-      </c>
-      <c r="H1883" t="inlineStr">
-        <is>
-          <t>Cadillac</t>
-        </is>
+      <c r="E1883" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1883" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1883" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1883" t="s">
+        <v>199</v>
       </c>
       <c r="I1883">
         <v>16</v>
@@ -65078,55 +64896,37 @@
       <c r="J1883">
         <v>0</v>
       </c>
-      <c r="K1883" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1883" t="inlineStr">
-        <is>
-          <t>1:37.179</t>
-        </is>
-      </c>
-    </row>
-    <row r="1884" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1884" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1884" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1884" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1883" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1883" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1884" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1884" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1884" t="s">
+        <v>204</v>
       </c>
       <c r="D1884">
         <v>8</v>
       </c>
-      <c r="E1884" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1884" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1884" t="inlineStr">
-        <is>
-          <t>Lance Stroll</t>
-        </is>
-      </c>
-      <c r="H1884" t="inlineStr">
-        <is>
-          <t>Aston Martin</t>
-        </is>
+      <c r="E1884" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1884" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1884" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1884" t="s">
+        <v>133</v>
       </c>
       <c r="I1884">
         <v>17</v>
@@ -65134,55 +64934,37 @@
       <c r="J1884">
         <v>0</v>
       </c>
-      <c r="K1884" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1884" t="inlineStr">
-        <is>
-          <t>1:37.916</t>
-        </is>
-      </c>
-    </row>
-    <row r="1885" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1885" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1885" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1885" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1884" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1884" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1885" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1885" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1885" t="s">
+        <v>204</v>
       </c>
       <c r="D1885">
         <v>8</v>
       </c>
-      <c r="E1885" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1885" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1885" t="inlineStr">
-        <is>
-          <t>Gabriel Bortoleto</t>
-        </is>
-      </c>
-      <c r="H1885" t="inlineStr">
-        <is>
-          <t>Audi</t>
-        </is>
+      <c r="E1885" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1885" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1885" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1885" t="s">
+        <v>198</v>
       </c>
       <c r="I1885">
         <v>18</v>
@@ -65190,55 +64972,37 @@
       <c r="J1885">
         <v>0</v>
       </c>
-      <c r="K1885" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1885" t="inlineStr">
-        <is>
-          <t>1:37.930</t>
-        </is>
-      </c>
-    </row>
-    <row r="1886" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1886" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1886" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1886" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1885" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1885" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1886" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1886" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1886" t="s">
+        <v>204</v>
       </c>
       <c r="D1886">
         <v>8</v>
       </c>
-      <c r="E1886" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1886" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1886" t="inlineStr">
-        <is>
-          <t>Sergio Perez</t>
-        </is>
-      </c>
-      <c r="H1886" t="inlineStr">
-        <is>
-          <t>Cadillac</t>
-        </is>
+      <c r="E1886" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1886" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1886" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1886" t="s">
+        <v>199</v>
       </c>
       <c r="I1886">
         <v>19</v>
@@ -65246,55 +65010,37 @@
       <c r="J1886">
         <v>0</v>
       </c>
-      <c r="K1886" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1886" t="inlineStr">
-        <is>
-          <t>1:39.014</t>
-        </is>
-      </c>
-    </row>
-    <row r="1887" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1887" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1887" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1887" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1886" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1886" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1887" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1887" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1887" t="s">
+        <v>204</v>
       </c>
       <c r="D1887">
         <v>8</v>
       </c>
-      <c r="E1887" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1887" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1887" t="inlineStr">
-        <is>
-          <t>Polingua</t>
-        </is>
-      </c>
-      <c r="H1887" t="inlineStr">
-        <is>
-          <t>Red Bull</t>
-        </is>
+      <c r="E1887" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1887" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1887" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1887" t="s">
+        <v>135</v>
       </c>
       <c r="I1887">
         <v>20</v>
@@ -65302,55 +65048,37 @@
       <c r="J1887">
         <v>0</v>
       </c>
-      <c r="K1887" t="inlineStr">
-        <is>
-          <t>DNF</t>
-        </is>
-      </c>
-      <c r="L1887" t="inlineStr">
-        <is>
-          <t>1:36.147</t>
-        </is>
-      </c>
-    </row>
-    <row r="1888" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1888" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1888" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1888" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1887" t="s">
+        <v>194</v>
+      </c>
+      <c r="L1887" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1888" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1888" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1888" t="s">
+        <v>204</v>
       </c>
       <c r="D1888">
         <v>8</v>
       </c>
-      <c r="E1888" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1888" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1888" t="inlineStr">
-        <is>
-          <t>Lando Norris</t>
-        </is>
-      </c>
-      <c r="H1888" t="inlineStr">
-        <is>
-          <t>McLaren</t>
-        </is>
+      <c r="E1888" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1888" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1888" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1888" t="s">
+        <v>143</v>
       </c>
       <c r="I1888">
         <v>21</v>
@@ -65358,55 +65086,37 @@
       <c r="J1888">
         <v>0</v>
       </c>
-      <c r="K1888" t="inlineStr">
-        <is>
-          <t>DNF</t>
-        </is>
-      </c>
-      <c r="L1888" t="inlineStr">
-        <is>
-          <t>1:35.788</t>
-        </is>
-      </c>
-    </row>
-    <row r="1889" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1889" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1889" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1889" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1888" t="s">
+        <v>194</v>
+      </c>
+      <c r="L1888" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1889" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1889" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1889" t="s">
+        <v>204</v>
       </c>
       <c r="D1889">
         <v>8</v>
       </c>
-      <c r="E1889" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1889" t="inlineStr">
-        <is>
-          <t>Japanese GP</t>
-        </is>
-      </c>
-      <c r="G1889" t="inlineStr">
-        <is>
-          <t>Pierre Gasly</t>
-        </is>
-      </c>
-      <c r="H1889" t="inlineStr">
-        <is>
-          <t>Alpine</t>
-        </is>
+      <c r="E1889" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1889" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1889" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1889" t="s">
+        <v>140</v>
       </c>
       <c r="I1889">
         <v>22</v>
@@ -65414,18 +65124,14 @@
       <c r="J1889">
         <v>0</v>
       </c>
-      <c r="K1889" t="inlineStr">
-        <is>
-          <t>DNF</t>
-        </is>
-      </c>
-      <c r="L1889" t="inlineStr">
-        <is>
-          <t>1:37.326</t>
-        </is>
-      </c>
-    </row>
-    <row r="1890" spans="6:10" x14ac:dyDescent="0.45">
+      <c r="K1889" t="s">
+        <v>194</v>
+      </c>
+      <c r="L1889" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1890" t="s">
         <v>37</v>
       </c>
@@ -65433,7 +65139,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1891" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1891" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1891" t="s">
         <v>37</v>
       </c>
@@ -65441,7 +65147,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1892" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1892" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1892" t="s">
         <v>37</v>
       </c>
@@ -65449,7 +65155,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1893" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1893" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1893" t="s">
         <v>37</v>
       </c>
@@ -65457,7 +65163,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1894" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1894" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1894" t="s">
         <v>37</v>
       </c>
@@ -65465,7 +65171,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1895" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1895" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1895" t="s">
         <v>37</v>
       </c>
@@ -65473,7 +65179,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1896" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1896" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1896" t="s">
         <v>37</v>
       </c>
@@ -65481,7 +65187,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1897" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1897" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1897" t="s">
         <v>37</v>
       </c>
@@ -65489,7 +65195,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1898" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1898" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1898" t="s">
         <v>37</v>
       </c>
@@ -65497,7 +65203,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1899" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1899" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1899" t="s">
         <v>37</v>
       </c>
@@ -65505,7 +65211,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1900" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1900" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1900" t="s">
         <v>37</v>
       </c>
@@ -65513,7 +65219,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1901" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1901" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1901" t="s">
         <v>37</v>
       </c>
@@ -65521,7 +65227,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1902" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1902" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1902" t="s">
         <v>37</v>
       </c>
@@ -65529,7 +65235,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1903" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1903" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1903" t="s">
         <v>37</v>
       </c>
@@ -65537,7 +65243,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1904" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1904" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1904" t="s">
         <v>37</v>
       </c>
@@ -89333,10 +89039,8 @@
         <f t="shared" si="5"/>
         <v>Suzuka International Racing Course</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
+      <c r="F28" t="s">
+        <v>190</v>
       </c>
       <c r="G28" s="11">
         <v>0.25</v>
@@ -89357,14 +89061,14 @@
         <v>9</v>
       </c>
       <c r="C29" s="8">
-        <v>46306</v>
+        <v>46320</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>166</v>
+        <v>117</v>
       </c>
       <c r="E29" t="str">
         <f t="shared" si="5"/>
-        <v>Marina Bay Street Circuit</v>
+        <v>Circuit of the Americas</v>
       </c>
       <c r="F29" t="s">
         <v>191</v>
@@ -89388,14 +89092,14 @@
         <v>10</v>
       </c>
       <c r="C30" s="8">
-        <v>46313</v>
-      </c>
-      <c r="D30" t="s">
-        <v>120</v>
+        <v>46327</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>169</v>
       </c>
       <c r="E30" t="str">
-        <f t="shared" si="5"/>
-        <v>Algarve International Circuit</v>
+        <f t="shared" ref="E30:E44" si="6">VLOOKUP(D30,$K$1:$L$43,2,FALSE)</f>
+        <v>Autódromo Hermanos Rodríguez</v>
       </c>
       <c r="F30" t="s">
         <v>191</v>
@@ -89419,14 +89123,14 @@
         <v>11</v>
       </c>
       <c r="C31" s="8">
-        <v>46320</v>
+        <v>46334</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="E31" t="str">
-        <f t="shared" ref="E31" si="6">VLOOKUP(D31,$K$1:$L$43,2,FALSE)</f>
-        <v>Circuit of the Americas</v>
+        <f t="shared" si="6"/>
+        <v>Autódromo José Carlos Pace (Interlagos)</v>
       </c>
       <c r="F31" t="s">
         <v>191</v>
@@ -89450,14 +89154,14 @@
         <v>12</v>
       </c>
       <c r="C32" s="8">
-        <v>46327</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>169</v>
+        <v>46341</v>
+      </c>
+      <c r="D32" t="s">
+        <v>123</v>
       </c>
       <c r="E32" t="str">
-        <f t="shared" si="5"/>
-        <v>Autódromo Hermanos Rodríguez</v>
+        <f t="shared" si="6"/>
+        <v>Red Bull Ring</v>
       </c>
       <c r="F32" t="s">
         <v>191</v>
@@ -89481,14 +89185,14 @@
         <v>13</v>
       </c>
       <c r="C33" s="8">
-        <v>46334</v>
+        <v>46348</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>171</v>
+        <v>115</v>
       </c>
       <c r="E33" t="str">
-        <f t="shared" si="5"/>
-        <v>Autódromo José Carlos Pace (Interlagos)</v>
+        <f t="shared" si="6"/>
+        <v>Las Vegas Strip Circuit</v>
       </c>
       <c r="F33" t="s">
         <v>191</v>
@@ -89512,14 +89216,14 @@
         <v>14</v>
       </c>
       <c r="C34" s="8">
-        <v>46341</v>
-      </c>
-      <c r="D34" t="s">
-        <v>123</v>
+        <v>46355</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="E34" t="str">
-        <f t="shared" si="5"/>
-        <v>Red Bull Ring</v>
+        <f t="shared" si="6"/>
+        <v>Lusail International Circuit</v>
       </c>
       <c r="F34" t="s">
         <v>191</v>
@@ -89543,14 +89247,14 @@
         <v>15</v>
       </c>
       <c r="C35" s="8">
-        <v>46348</v>
+        <v>46362</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E35" t="str">
-        <f t="shared" si="5"/>
-        <v>Las Vegas Strip Circuit</v>
+        <f t="shared" si="6"/>
+        <v>Yas Marina Circuit</v>
       </c>
       <c r="F35" t="s">
         <v>191</v>
@@ -89568,14 +89272,14 @@
         <v>16</v>
       </c>
       <c r="C36" s="8">
-        <v>46355</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>118</v>
+        <v>46369</v>
+      </c>
+      <c r="D36" t="s">
+        <v>125</v>
       </c>
       <c r="E36" t="str">
-        <f t="shared" si="5"/>
-        <v>Lusail International Circuit</v>
+        <f t="shared" si="6"/>
+        <v>Circuit Zandvoort</v>
       </c>
       <c r="F36" t="s">
         <v>191</v>
@@ -89593,14 +89297,14 @@
         <v>17</v>
       </c>
       <c r="C37" s="8">
-        <v>46362</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>126</v>
+        <v>46376</v>
+      </c>
+      <c r="D37" t="s">
+        <v>163</v>
       </c>
       <c r="E37" t="str">
-        <f t="shared" si="5"/>
-        <v>Yas Marina Circuit</v>
+        <f t="shared" si="6"/>
+        <v>Autodromo Nazionale Monza</v>
       </c>
       <c r="F37" t="s">
         <v>191</v>
@@ -89618,14 +89322,14 @@
         <v>18</v>
       </c>
       <c r="C38" s="8">
-        <v>46369</v>
+        <v>46383</v>
       </c>
       <c r="D38" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E38" t="str">
-        <f t="shared" si="5"/>
-        <v>Circuit Zandvoort</v>
+        <f t="shared" si="6"/>
+        <v>Madring</v>
       </c>
       <c r="F38" t="s">
         <v>191</v>
@@ -89643,14 +89347,14 @@
         <v>19</v>
       </c>
       <c r="C39" s="8">
-        <v>46376</v>
+        <v>46390</v>
       </c>
       <c r="D39" t="s">
-        <v>163</v>
+        <v>20</v>
       </c>
       <c r="E39" t="str">
-        <f t="shared" si="5"/>
-        <v>Autodromo Nazionale Monza</v>
+        <f t="shared" si="6"/>
+        <v>Miami International Autodrome</v>
       </c>
       <c r="F39" t="s">
         <v>191</v>
@@ -89668,14 +89372,14 @@
         <v>20</v>
       </c>
       <c r="C40" s="8">
-        <v>46383</v>
-      </c>
-      <c r="D40" t="s">
-        <v>113</v>
+        <v>46397</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="E40" t="str">
-        <f t="shared" si="5"/>
-        <v>Madring</v>
+        <f t="shared" si="6"/>
+        <v>Baku City Circuit</v>
       </c>
       <c r="F40" t="s">
         <v>191</v>
@@ -89693,14 +89397,14 @@
         <v>21</v>
       </c>
       <c r="C41" s="8">
-        <v>46390</v>
+        <v>46404</v>
       </c>
       <c r="D41" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E41" t="str">
-        <f t="shared" si="5"/>
-        <v>Miami International Autodrome</v>
+        <f>VLOOKUP(D41,$K$1:$L$43,2,FALSE)</f>
+        <v>Autodromo Enzo e Dino Ferrari (Imola)</v>
       </c>
       <c r="F41" t="s">
         <v>191</v>
@@ -89718,14 +89422,14 @@
         <v>22</v>
       </c>
       <c r="C42" s="8">
-        <v>46397</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>119</v>
+        <v>46411</v>
+      </c>
+      <c r="D42" t="s">
+        <v>15</v>
       </c>
       <c r="E42" t="str">
-        <f t="shared" ref="E42" si="7">VLOOKUP(D42,$K$1:$L$43,2,FALSE)</f>
-        <v>Baku City Circuit</v>
+        <f>VLOOKUP(D42,$K$1:$L$43,2,FALSE)</f>
+        <v>Bahrain International Circuit</v>
       </c>
       <c r="F42" t="s">
         <v>191</v>
@@ -89735,57 +89439,59 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A43" t="str">
-        <v>Teikirise</v>
-      </c>
-      <c r="B43" t="n">
+      <c r="A43" t="s">
+        <v>204</v>
+      </c>
+      <c r="B43">
         <f>B42+1</f>
         <v>23</v>
       </c>
-      <c r="C43" t="n" s="8">
-        <v>46404</v>
-      </c>
-      <c r="D43" t="str">
-        <v>Emilia Romagna GP</v>
+      <c r="C43" s="8">
+        <v>46418</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>166</v>
       </c>
       <c r="E43" t="str">
-        <f>VLOOKUP(D43,$K$1:$L$43,2,FALSE)</f>
-        <v>Autodromo Enzo e Dino Ferrari (Imola)</v>
-      </c>
-      <c r="F43" t="str">
-        <v>Upcoming</v>
-      </c>
-      <c r="G43" t="n" s="11">
+        <f t="shared" ref="E43:E44" si="7">VLOOKUP(D43,$K$1:$L$43,2,FALSE)</f>
+        <v>Marina Bay Street Circuit</v>
+      </c>
+      <c r="F43" t="s">
+        <v>191</v>
+      </c>
+      <c r="G43" s="11">
         <v>0.25</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A44" t="str">
-        <v>Teikirise</v>
-      </c>
-      <c r="B44" t="n">
+      <c r="A44" t="s">
+        <v>204</v>
+      </c>
+      <c r="B44">
         <f>B43+1</f>
         <v>24</v>
       </c>
-      <c r="C44" t="n" s="8">
-        <v>46411</v>
-      </c>
-      <c r="D44" t="str">
-        <v>Bahrain GP</v>
+      <c r="C44" s="8">
+        <v>46425</v>
+      </c>
+      <c r="D44" t="s">
+        <v>120</v>
       </c>
       <c r="E44" t="str">
-        <f>VLOOKUP(D44,$K$1:$L$43,2,FALSE)</f>
-        <v>Bahrain International Circuit</v>
-      </c>
-      <c r="F44" t="str">
-        <v>Upcoming</v>
-      </c>
-      <c r="G44" t="n" s="11">
+        <f t="shared" si="7"/>
+        <v>Algarve International Circuit</v>
+      </c>
+      <c r="F44" t="s">
+        <v>191</v>
+      </c>
+      <c r="G44" s="11">
         <v>0.25</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C45" s="8"/>
+      <c r="D45" s="6"/>
+      <c r="G45" s="11"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C46" s="8"/>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ruiro\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE8B375-D277-4CB3-99D4-0570098D3F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D03C874-154C-4E7A-998A-E18281187A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Leagues" sheetId="10" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19748" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19880" uniqueCount="529">
   <si>
     <t>Lewis Hamilton</t>
   </si>
@@ -1558,6 +1558,93 @@
   <si>
     <t>1:37.326</t>
   </si>
+  <si>
+    <t>95:55.647</t>
+  </si>
+  <si>
+    <t>+5.751</t>
+  </si>
+  <si>
+    <t>+53.336</t>
+  </si>
+  <si>
+    <t>1:37.309</t>
+  </si>
+  <si>
+    <t>1:38.877</t>
+  </si>
+  <si>
+    <t>1:39.733</t>
+  </si>
+  <si>
+    <t>1:40.793</t>
+  </si>
+  <si>
+    <t>1:40.816</t>
+  </si>
+  <si>
+    <t>1:40.419</t>
+  </si>
+  <si>
+    <t>1:40.353</t>
+  </si>
+  <si>
+    <t>1:41.402</t>
+  </si>
+  <si>
+    <t>1:41.180</t>
+  </si>
+  <si>
+    <t>1:41.120</t>
+  </si>
+  <si>
+    <t>1:41.831</t>
+  </si>
+  <si>
+    <t>1:41.115</t>
+  </si>
+  <si>
+    <t>1:42.207</t>
+  </si>
+  <si>
+    <t>1:42.081</t>
+  </si>
+  <si>
+    <t>1:42.086</t>
+  </si>
+  <si>
+    <t>1:42.128</t>
+  </si>
+  <si>
+    <t>1:42.689</t>
+  </si>
+  <si>
+    <t>1:42.858</t>
+  </si>
+  <si>
+    <t>1:42.930</t>
+  </si>
+  <si>
+    <t>1:38.253</t>
+  </si>
+  <si>
+    <t>1:40.805</t>
+  </si>
+  <si>
+    <t>1:41.752</t>
+  </si>
+  <si>
+    <t>+1:02.302</t>
+  </si>
+  <si>
+    <t>+1:03.650</t>
+  </si>
+  <si>
+    <t>+1:05.872</t>
+  </si>
+  <si>
+    <t>+1:25.664</t>
+  </si>
 </sst>
 </file>
 
@@ -65132,182 +65219,864 @@
       </c>
     </row>
     <row r="1890" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1890" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1890" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1890" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1890">
+        <v>9</v>
+      </c>
+      <c r="E1890" t="s">
+        <v>206</v>
+      </c>
       <c r="F1890" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1890" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="G1890" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1890" t="str">
+        <f t="shared" ref="H1890:H1911" si="5">VLOOKUP(G1890,$O$1761:$P$1785,2,FALSE)</f>
+        <v>McLaren</v>
+      </c>
+      <c r="I1890">
+        <v>1</v>
+      </c>
+      <c r="J1890">
+        <v>25</v>
+      </c>
+      <c r="K1890" s="12" t="s">
+        <v>500</v>
+      </c>
+      <c r="L1890" s="12" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="1891" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1891" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1891" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1891" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1891">
+        <v>9</v>
+      </c>
+      <c r="E1891" t="s">
+        <v>206</v>
+      </c>
       <c r="F1891" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1891" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="G1891" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1891" t="str">
+        <f t="shared" si="5"/>
+        <v>Mercedes</v>
+      </c>
+      <c r="I1891">
+        <v>2</v>
+      </c>
+      <c r="J1891">
+        <v>18</v>
+      </c>
+      <c r="K1891" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="L1891" s="12" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="1892" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1892" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1892" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1892" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1892">
+        <v>9</v>
+      </c>
+      <c r="E1892" t="s">
+        <v>206</v>
+      </c>
       <c r="F1892" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1892" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="G1892" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1892" t="str">
+        <f t="shared" si="5"/>
+        <v>McLaren</v>
+      </c>
+      <c r="I1892">
+        <v>3</v>
+      </c>
+      <c r="J1892">
+        <v>15</v>
+      </c>
+      <c r="K1892" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="L1892" s="12" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="1893" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1893" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1893" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1893" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1893">
+        <v>9</v>
+      </c>
+      <c r="E1893" t="s">
+        <v>206</v>
+      </c>
       <c r="F1893" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1893" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="G1893" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1893" t="str">
+        <f t="shared" si="5"/>
+        <v>Ferrari</v>
+      </c>
+      <c r="I1893">
+        <v>4</v>
+      </c>
+      <c r="J1893">
+        <v>12</v>
+      </c>
+      <c r="K1893" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="L1893" s="12" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="1894" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1894" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1894" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1894" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1894">
+        <v>9</v>
+      </c>
+      <c r="E1894" t="s">
+        <v>206</v>
+      </c>
       <c r="F1894" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1894" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="G1894" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1894" t="str">
+        <f t="shared" si="5"/>
+        <v>Red Bull</v>
+      </c>
+      <c r="I1894">
+        <v>5</v>
+      </c>
+      <c r="J1894">
+        <v>10</v>
+      </c>
+      <c r="K1894" s="12" t="s">
+        <v>526</v>
+      </c>
+      <c r="L1894" s="12" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="1895" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1895" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1895" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1895" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1895">
+        <v>9</v>
+      </c>
+      <c r="E1895" t="s">
+        <v>206</v>
+      </c>
       <c r="F1895" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1895" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="G1895" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1895" t="str">
+        <f t="shared" si="5"/>
+        <v>Ferrari</v>
+      </c>
+      <c r="I1895">
+        <v>6</v>
+      </c>
+      <c r="J1895">
+        <v>8</v>
+      </c>
+      <c r="K1895" s="12" t="s">
+        <v>527</v>
+      </c>
+      <c r="L1895" s="12" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="1896" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1896" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1896" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1896" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1896">
+        <v>9</v>
+      </c>
+      <c r="E1896" t="s">
+        <v>206</v>
+      </c>
       <c r="F1896" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1896" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="G1896" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1896" t="str">
+        <f t="shared" si="5"/>
+        <v>Mercedes</v>
+      </c>
+      <c r="I1896">
+        <v>7</v>
+      </c>
+      <c r="J1896">
+        <v>6</v>
+      </c>
+      <c r="K1896" s="12" t="s">
+        <v>528</v>
+      </c>
+      <c r="L1896" s="12" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="1897" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1897" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1897" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1897" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1897">
+        <v>9</v>
+      </c>
+      <c r="E1897" t="s">
+        <v>206</v>
+      </c>
       <c r="F1897" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1897" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="G1897" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1897" t="str">
+        <f t="shared" si="5"/>
+        <v>Williams</v>
+      </c>
+      <c r="I1897">
+        <v>8</v>
+      </c>
+      <c r="J1897">
+        <v>4</v>
+      </c>
+      <c r="K1897" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1897" s="12" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="1898" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1898" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1898" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1898" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1898">
+        <v>9</v>
+      </c>
+      <c r="E1898" t="s">
+        <v>206</v>
+      </c>
       <c r="F1898" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1898" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="G1898" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1898" t="str">
+        <f t="shared" si="5"/>
+        <v>Alpine</v>
+      </c>
+      <c r="I1898">
+        <v>9</v>
+      </c>
+      <c r="J1898">
+        <v>2</v>
+      </c>
+      <c r="K1898" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1898" s="12" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="1899" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1899" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1899" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1899" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1899">
+        <v>9</v>
+      </c>
+      <c r="E1899" t="s">
+        <v>206</v>
+      </c>
       <c r="F1899" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1899" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="G1899" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1899" t="str">
+        <f t="shared" si="5"/>
+        <v>Williams</v>
+      </c>
+      <c r="I1899">
+        <v>10</v>
+      </c>
+      <c r="J1899">
+        <v>1</v>
+      </c>
+      <c r="K1899" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1899" s="12" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="1900" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1900" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1900" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1900" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1900">
+        <v>9</v>
+      </c>
+      <c r="E1900" t="s">
+        <v>206</v>
+      </c>
       <c r="F1900" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1900" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="G1900" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1900" t="str">
+        <f t="shared" si="5"/>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="I1900">
+        <v>11</v>
+      </c>
+      <c r="J1900">
+        <v>0</v>
+      </c>
+      <c r="K1900" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1900" s="12" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="1901" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1901" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1901" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1901" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1901">
+        <v>9</v>
+      </c>
+      <c r="E1901" t="s">
+        <v>206</v>
+      </c>
       <c r="F1901" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1901" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="G1901" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1901" t="str">
+        <f t="shared" si="5"/>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="I1901">
+        <v>12</v>
+      </c>
+      <c r="J1901">
+        <v>0</v>
+      </c>
+      <c r="K1901" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1901" s="12" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="1902" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1902" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1902" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1902" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1902">
+        <v>9</v>
+      </c>
+      <c r="E1902" t="s">
+        <v>206</v>
+      </c>
       <c r="F1902" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1902" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="G1902" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1902" t="str">
+        <f t="shared" si="5"/>
+        <v>Aston Martin</v>
+      </c>
+      <c r="I1902">
+        <v>13</v>
+      </c>
+      <c r="J1902">
+        <v>0</v>
+      </c>
+      <c r="K1902" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1902" s="12" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="1903" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1903" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1903" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1903" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1903">
+        <v>9</v>
+      </c>
+      <c r="E1903" t="s">
+        <v>206</v>
+      </c>
       <c r="F1903" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1903" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="G1903" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1903" t="str">
+        <f t="shared" si="5"/>
+        <v>Haas</v>
+      </c>
+      <c r="I1903">
+        <v>14</v>
+      </c>
+      <c r="J1903">
+        <v>0</v>
+      </c>
+      <c r="K1903" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1903" s="12" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="1904" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1904" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1904" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1904" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1904">
+        <v>9</v>
+      </c>
+      <c r="E1904" t="s">
+        <v>206</v>
+      </c>
       <c r="F1904" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1904" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1905" spans="6:10" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+      <c r="G1904" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1904" t="str">
+        <f t="shared" si="5"/>
+        <v>Haas</v>
+      </c>
+      <c r="I1904">
+        <v>15</v>
+      </c>
+      <c r="J1904">
+        <v>0</v>
+      </c>
+      <c r="K1904" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1904" s="12" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1905" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1905" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1905" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1905">
+        <v>9</v>
+      </c>
+      <c r="E1905" t="s">
+        <v>206</v>
+      </c>
       <c r="F1905" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1905" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1906" spans="6:10" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+      <c r="G1905" t="s">
+        <v>201</v>
+      </c>
+      <c r="H1905" t="str">
+        <f t="shared" si="5"/>
+        <v>Alpine</v>
+      </c>
+      <c r="I1905">
+        <v>16</v>
+      </c>
+      <c r="J1905">
+        <v>0</v>
+      </c>
+      <c r="K1905" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1905" s="12" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1906" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1906" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1906" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1906">
+        <v>9</v>
+      </c>
+      <c r="E1906" t="s">
+        <v>206</v>
+      </c>
       <c r="F1906" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1906" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1907" spans="6:10" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+      <c r="G1906" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1906" t="str">
+        <f t="shared" si="5"/>
+        <v>Cadillac</v>
+      </c>
+      <c r="I1906">
+        <v>17</v>
+      </c>
+      <c r="J1906">
+        <v>0</v>
+      </c>
+      <c r="K1906" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1906" s="12" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1907" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1907" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1907" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1907">
+        <v>9</v>
+      </c>
+      <c r="E1907" t="s">
+        <v>206</v>
+      </c>
       <c r="F1907" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1907" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1908" spans="6:10" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+      <c r="G1907" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1907" t="str">
+        <f t="shared" si="5"/>
+        <v>Cadillac</v>
+      </c>
+      <c r="I1907">
+        <v>18</v>
+      </c>
+      <c r="J1907">
+        <v>0</v>
+      </c>
+      <c r="K1907" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1907" s="12" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1908" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1908" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1908" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1908">
+        <v>9</v>
+      </c>
+      <c r="E1908" t="s">
+        <v>206</v>
+      </c>
       <c r="F1908" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1908" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1909" spans="6:10" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+      <c r="G1908" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1908" t="str">
+        <f t="shared" si="5"/>
+        <v>Audi</v>
+      </c>
+      <c r="I1908">
+        <v>19</v>
+      </c>
+      <c r="J1908">
+        <v>0</v>
+      </c>
+      <c r="K1908" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1908" s="12" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1909" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1909" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1909" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1909">
+        <v>9</v>
+      </c>
+      <c r="E1909" t="s">
+        <v>206</v>
+      </c>
       <c r="F1909" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1909" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1910" spans="6:10" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+      <c r="G1909" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1909" t="str">
+        <f t="shared" si="5"/>
+        <v>Aston Martin</v>
+      </c>
+      <c r="I1909">
+        <v>20</v>
+      </c>
+      <c r="J1909">
+        <v>0</v>
+      </c>
+      <c r="K1909" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1909" s="12" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1910" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1910" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1910" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1910">
+        <v>9</v>
+      </c>
+      <c r="E1910" t="s">
+        <v>206</v>
+      </c>
       <c r="F1910" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1910" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1911" spans="6:10" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+      <c r="G1910" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1910" t="str">
+        <f t="shared" si="5"/>
+        <v>Red Bull</v>
+      </c>
+      <c r="I1910">
+        <v>21</v>
+      </c>
+      <c r="J1910">
+        <v>0</v>
+      </c>
+      <c r="K1910" t="s">
+        <v>194</v>
+      </c>
+      <c r="L1910" s="12" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1911" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1911" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1911" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1911">
+        <v>9</v>
+      </c>
+      <c r="E1911" t="s">
+        <v>206</v>
+      </c>
       <c r="F1911" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1911" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1912" spans="6:10" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+      <c r="G1911" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1911" t="str">
+        <f t="shared" si="5"/>
+        <v>Audi</v>
+      </c>
+      <c r="I1911">
+        <v>22</v>
+      </c>
+      <c r="J1911">
+        <v>0</v>
+      </c>
+      <c r="K1911" t="s">
+        <v>194</v>
+      </c>
+      <c r="L1911" s="12" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1912" t="s">
         <v>37</v>
       </c>
@@ -65315,7 +66084,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1913" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1913" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1913" t="s">
         <v>37</v>
       </c>
@@ -65323,7 +66092,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1914" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1914" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1914" t="s">
         <v>37</v>
       </c>
@@ -65331,7 +66100,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1915" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1915" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1915" t="s">
         <v>37</v>
       </c>
@@ -65339,7 +66108,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1916" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1916" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1916" t="s">
         <v>37</v>
       </c>
@@ -65347,7 +66116,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1917" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1917" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1917" t="s">
         <v>37</v>
       </c>
@@ -65355,7 +66124,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1918" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1918" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1918" t="s">
         <v>37</v>
       </c>
@@ -65363,7 +66132,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1919" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1919" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1919" t="s">
         <v>37</v>
       </c>
@@ -65371,7 +66140,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1920" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1920" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1920" t="s">
         <v>37</v>
       </c>
@@ -88974,7 +89743,7 @@
         <v>430</v>
       </c>
       <c r="E26" t="str">
-        <f t="shared" ref="E26:E41" si="5">VLOOKUP(D26,$K$1:$L$43,2,FALSE)</f>
+        <f t="shared" ref="E26:E29" si="5">VLOOKUP(D26,$K$1:$L$43,2,FALSE)</f>
         <v>Circuit de Barcelona-Catalunya</v>
       </c>
       <c r="F26" t="s">
@@ -89071,7 +89840,7 @@
         <v>Circuit of the Americas</v>
       </c>
       <c r="F29" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G29" s="11">
         <v>0.25</v>
@@ -89098,7 +89867,7 @@
         <v>169</v>
       </c>
       <c r="E30" t="str">
-        <f t="shared" ref="E30:E44" si="6">VLOOKUP(D30,$K$1:$L$43,2,FALSE)</f>
+        <f t="shared" ref="E30:E40" si="6">VLOOKUP(D30,$K$1:$L$43,2,FALSE)</f>
         <v>Autódromo Hermanos Rodríguez</v>
       </c>
       <c r="F30" t="s">

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -65234,8 +65234,10 @@
       <c r="E1890" t="s">
         <v>206</v>
       </c>
-      <c r="F1890" t="s">
-        <v>17</v>
+      <c r="F1890" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1890" t="s">
         <v>32</v>
@@ -65273,8 +65275,10 @@
       <c r="E1891" t="s">
         <v>206</v>
       </c>
-      <c r="F1891" t="s">
-        <v>17</v>
+      <c r="F1891" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1891" t="s">
         <v>34</v>
@@ -65312,8 +65316,10 @@
       <c r="E1892" t="s">
         <v>206</v>
       </c>
-      <c r="F1892" t="s">
-        <v>17</v>
+      <c r="F1892" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1892" t="s">
         <v>3</v>
@@ -65351,8 +65357,10 @@
       <c r="E1893" t="s">
         <v>206</v>
       </c>
-      <c r="F1893" t="s">
-        <v>17</v>
+      <c r="F1893" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1893" t="s">
         <v>0</v>
@@ -65390,8 +65398,10 @@
       <c r="E1894" t="s">
         <v>206</v>
       </c>
-      <c r="F1894" t="s">
-        <v>17</v>
+      <c r="F1894" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1894" t="s">
         <v>1</v>
@@ -65429,8 +65439,10 @@
       <c r="E1895" t="s">
         <v>206</v>
       </c>
-      <c r="F1895" t="s">
-        <v>17</v>
+      <c r="F1895" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1895" t="s">
         <v>2</v>
@@ -65468,8 +65480,10 @@
       <c r="E1896" t="s">
         <v>206</v>
       </c>
-      <c r="F1896" t="s">
-        <v>17</v>
+      <c r="F1896" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1896" t="s">
         <v>200</v>
@@ -65507,8 +65521,10 @@
       <c r="E1897" t="s">
         <v>206</v>
       </c>
-      <c r="F1897" t="s">
-        <v>17</v>
+      <c r="F1897" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1897" t="s">
         <v>12</v>
@@ -65546,8 +65562,10 @@
       <c r="E1898" t="s">
         <v>206</v>
       </c>
-      <c r="F1898" t="s">
-        <v>17</v>
+      <c r="F1898" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1898" t="s">
         <v>8</v>
@@ -65585,8 +65603,10 @@
       <c r="E1899" t="s">
         <v>206</v>
       </c>
-      <c r="F1899" t="s">
-        <v>17</v>
+      <c r="F1899" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1899" t="s">
         <v>5</v>
@@ -65624,8 +65644,10 @@
       <c r="E1900" t="s">
         <v>206</v>
       </c>
-      <c r="F1900" t="s">
-        <v>17</v>
+      <c r="F1900" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1900" t="s">
         <v>202</v>
@@ -65663,8 +65685,10 @@
       <c r="E1901" t="s">
         <v>206</v>
       </c>
-      <c r="F1901" t="s">
-        <v>17</v>
+      <c r="F1901" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1901" t="s">
         <v>13</v>
@@ -65702,8 +65726,10 @@
       <c r="E1902" t="s">
         <v>206</v>
       </c>
-      <c r="F1902" t="s">
-        <v>17</v>
+      <c r="F1902" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1902" t="s">
         <v>6</v>
@@ -65741,8 +65767,10 @@
       <c r="E1903" t="s">
         <v>206</v>
       </c>
-      <c r="F1903" t="s">
-        <v>17</v>
+      <c r="F1903" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1903" t="s">
         <v>14</v>
@@ -65780,8 +65808,10 @@
       <c r="E1904" t="s">
         <v>206</v>
       </c>
-      <c r="F1904" t="s">
-        <v>17</v>
+      <c r="F1904" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1904" t="s">
         <v>9</v>
@@ -65819,8 +65849,10 @@
       <c r="E1905" t="s">
         <v>206</v>
       </c>
-      <c r="F1905" t="s">
-        <v>17</v>
+      <c r="F1905" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1905" t="s">
         <v>201</v>
@@ -65858,8 +65890,10 @@
       <c r="E1906" t="s">
         <v>206</v>
       </c>
-      <c r="F1906" t="s">
-        <v>17</v>
+      <c r="F1906" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1906" t="s">
         <v>55</v>
@@ -65897,8 +65931,10 @@
       <c r="E1907" t="s">
         <v>206</v>
       </c>
-      <c r="F1907" t="s">
-        <v>17</v>
+      <c r="F1907" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1907" t="s">
         <v>79</v>
@@ -65936,8 +65972,10 @@
       <c r="E1908" t="s">
         <v>206</v>
       </c>
-      <c r="F1908" t="s">
-        <v>17</v>
+      <c r="F1908" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1908" t="s">
         <v>35</v>
@@ -65975,8 +66013,10 @@
       <c r="E1909" t="s">
         <v>206</v>
       </c>
-      <c r="F1909" t="s">
-        <v>17</v>
+      <c r="F1909" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1909" t="s">
         <v>11</v>
@@ -66014,8 +66054,10 @@
       <c r="E1910" t="s">
         <v>206</v>
       </c>
-      <c r="F1910" t="s">
-        <v>17</v>
+      <c r="F1910" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1910" t="s">
         <v>33</v>
@@ -66053,8 +66095,10 @@
       <c r="E1911" t="s">
         <v>206</v>
       </c>
-      <c r="F1911" t="s">
-        <v>17</v>
+      <c r="F1911" t="inlineStr">
+        <is>
+          <t>United States GP</t>
+        </is>
       </c>
       <c r="G1911" t="s">
         <v>10</v>
